--- a/通用/房屋说明-官田村.xlsx
+++ b/通用/房屋说明-官田村.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20260" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20240" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="房屋说明" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="宋体"/>
       <family val="2"/>
@@ -33,10 +33,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,7 +53,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE599"/>
+        <fgColor rgb="FFFFE599"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -61,10 +74,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -431,45 +447,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28.1640625" customWidth="1" min="7" max="7"/>
-    <col width="46.5" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>房号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>是否在租</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>打通房</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>收款人</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>水单价</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>电单价</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>水保底度数</t>
         </is>
@@ -526,7 +553,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>水电合并入105，本房号无独立读数</t>
+          <t>与105打通合算，水电合并入105</t>
         </is>
       </c>
     </row>
@@ -551,7 +578,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>与103打通合算，记为103+105</t>
+          <t>与103打通合算，水电表数=103+105</t>
         </is>
       </c>
     </row>
@@ -569,15 +596,10 @@
           <t>张</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>水：5元/度。保底2度。</t>
-        </is>
-      </c>
       <c r="F6" t="n">
         <v>5</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -698,11 +720,6 @@
       <c r="D14" t="inlineStr">
         <is>
           <t>张</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>水：6元/度。保底1度。</t>
         </is>
       </c>
     </row>
@@ -838,14 +855,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="2" max="3"/>
+    <col width="8" customWidth="1" min="4" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
@@ -973,7 +987,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>初始基准（水电合并入105，本房号无独立读数）</t>
+          <t>初始基准（与105合算，本房号无独立读数）</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1020,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>初始基准（与103打通合算，记为103+105）</t>
+          <t>初始基准（与103打通合算，水电表=103+105）</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1053,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>初始基准（水：5元/度。保底2度。）</t>
+          <t>初始基准</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1317,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>初始基准（水：6元/度。保底1度。）</t>
+          <t>初始基准</t>
         </is>
       </c>
     </row>

--- a/通用/房屋说明-官田村.xlsx
+++ b/通用/房屋说明-官田村.xlsx
@@ -854,7 +854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1453,6 +1453,39 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>陈桂红</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E19" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1日-30日</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>换租客（韦月芳→陈桂红）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
